--- a/main/ig/StructureDefinition-MESObservationBodyTemperature.xlsx
+++ b/main/ig/StructureDefinition-MESObservationBodyTemperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T14:10:46+00:00</t>
+    <t>2026-03-12T14:12:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,7 +667,7 @@
     <t>MesReasonForMeasurement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.2.0}
 </t>
   </si>
   <si>
@@ -1701,7 +1701,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J151-BodySiteBodyTemperature-ENS/FHIR/JDV-J151-BodySiteBodyTemperature-ENS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J151-BodySiteBodyTemperature-ENS/FHIR/JDV-J151-BodySiteBodyTemperature-ENS|20240927120000</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1767,7 +1767,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J152-MethodBodyTemperature-ENS/FHIR/JDV-J152-MethodBodyTemperature-ENS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J152-MethodBodyTemperature-ENS/FHIR/JDV-J152-MethodBodyTemperature-ENS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J152-MethodBodyTemperature-ENS/FHIR/JDV-J152-MethodBodyTemperature-ENS|20240726120000</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2533,7 +2533,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="93.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="98.07421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="110.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-MESObservationBodyTemperature.xlsx
+++ b/main/ig/StructureDefinition-MESObservationBodyTemperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T14:12:24+00:00</t>
+    <t>2026-03-12T14:18:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
